--- a/verification/model_verification_results_57_buses.xlsx
+++ b/verification/model_verification_results_57_buses.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>checkpoint_57_25_False_vr_vi_final.pt_0.00</t>
   </si>
@@ -139,16 +139,34 @@
     <t>Vm Up Avg Violation</t>
   </si>
   <si>
+    <t>Vmg Up Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg Up Avg Violation</t>
+  </si>
+  <si>
     <t>Vm Down Max Violation</t>
   </si>
   <si>
     <t>Vm Down Avg Violation</t>
   </si>
   <si>
+    <t>Vmg Down Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg Down Avg Violation</t>
+  </si>
+  <si>
     <t>Vm tot Max Violation</t>
   </si>
   <si>
     <t>Vm tot Avg Violation</t>
+  </si>
+  <si>
+    <t>Vmg tot Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg tot Avg Violation</t>
   </si>
   <si>
     <t>Ibal tot Max Violation</t>
@@ -512,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -600,22 +618,22 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>99.09849898267518</v>
+        <v>100.0004750000594</v>
       </c>
       <c r="D2">
-        <v>98.32756541986262</v>
+        <v>99.98582499822813</v>
       </c>
       <c r="E2">
-        <v>98.11434893815326</v>
+        <v>99.97403749675469</v>
       </c>
       <c r="F2">
-        <v>98.00756000017395</v>
+        <v>99.9676312459539</v>
       </c>
       <c r="G2">
-        <v>97.97017100869606</v>
+        <v>99.96407499550938</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -636,37 +654,37 @@
         <v>100</v>
       </c>
       <c r="O2">
-        <v>77.99537919778342</v>
+        <v>79.46655084821552</v>
       </c>
       <c r="P2">
-        <v>59.60731026324105</v>
+        <v>62.53289023638301</v>
       </c>
       <c r="Q2">
-        <v>49.97778549219008</v>
+        <v>53.52163837379682</v>
       </c>
       <c r="R2">
-        <v>45.03429606199249</v>
+        <v>48.35000569954787</v>
       </c>
       <c r="S2">
-        <v>41.61600189852994</v>
+        <v>44.74268805065912</v>
       </c>
       <c r="T2">
         <v>100</v>
       </c>
       <c r="U2">
-        <v>88.35586730755475</v>
+        <v>90.81982484707055</v>
       </c>
       <c r="V2">
-        <v>82.62539166216337</v>
+        <v>84.93403605190666</v>
       </c>
       <c r="W2">
-        <v>77.81335417100422</v>
+        <v>79.99158087001723</v>
       </c>
       <c r="X2">
-        <v>73.5811136441929</v>
+        <v>75.64240021524952</v>
       </c>
       <c r="Y2">
-        <v>69.78063434291694</v>
+        <v>71.73563434328398</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -677,22 +695,22 @@
         <v>100</v>
       </c>
       <c r="C3">
-        <v>99.95342913085014</v>
+        <v>99.96511377753832</v>
       </c>
       <c r="D3">
-        <v>99.9178965884324</v>
+        <v>99.92726410177075</v>
       </c>
       <c r="E3">
-        <v>99.89878098016968</v>
+        <v>99.89786714513725</v>
       </c>
       <c r="F3">
-        <v>99.89104103290252</v>
+        <v>99.88114926720489</v>
       </c>
       <c r="G3">
-        <v>99.88653699579226</v>
+        <v>99.86940799018285</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -713,37 +731,37 @@
         <v>100</v>
       </c>
       <c r="O3">
-        <v>67.64363855499866</v>
+        <v>69.47526776288542</v>
       </c>
       <c r="P3">
-        <v>43.36819003123875</v>
+        <v>47.30484666381318</v>
       </c>
       <c r="Q3">
-        <v>32.5876053792009</v>
+        <v>36.70065875425671</v>
       </c>
       <c r="R3">
-        <v>27.05565295550431</v>
+        <v>30.972673123466</v>
       </c>
       <c r="S3">
-        <v>24.23326079407061</v>
+        <v>27.94227133682903</v>
       </c>
       <c r="T3">
         <v>100</v>
       </c>
       <c r="U3">
-        <v>82.16726832665829</v>
+        <v>85.11255360273513</v>
       </c>
       <c r="V3">
-        <v>72.87567247499517</v>
+        <v>75.77223754692515</v>
       </c>
       <c r="W3">
-        <v>65.44282891414245</v>
+        <v>68.05655786667185</v>
       </c>
       <c r="X3">
-        <v>60.56695470540453</v>
+        <v>62.98769990238596</v>
       </c>
       <c r="Y3">
-        <v>56.43532974244157</v>
+        <v>58.6911341197496</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -754,52 +772,52 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>99.09526775484764</v>
+        <v>99.96426700801663</v>
       </c>
       <c r="D4">
-        <v>98.5700404176191</v>
+        <v>99.9471536737416</v>
       </c>
       <c r="E4">
-        <v>98.19029026831308</v>
+        <v>99.93454055885225</v>
       </c>
       <c r="F4">
-        <v>98.12449200546814</v>
+        <v>99.92809649470412</v>
       </c>
       <c r="G4">
-        <v>98.09071000506975</v>
+        <v>99.92443381614854</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>78.40826156014585</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>72.12709532465908</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>68.29346930603116</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>65.51382690705113</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>63.13988668765981</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>54.61183361621283</v>
+        <v>64.63341586866491</v>
       </c>
       <c r="P4">
-        <v>26.02459616974857</v>
+        <v>33.21560432754304</v>
       </c>
       <c r="Q4">
-        <v>8.743131713209436</v>
+        <v>11.99432947252919</v>
       </c>
       <c r="R4">
-        <v>1.919679252848245</v>
+        <v>2.773468095264907</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -808,16 +826,16 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>58.54885552240142</v>
+        <v>61.1870441876865</v>
       </c>
       <c r="V4">
-        <v>55.98296024890279</v>
+        <v>40.10501855813961</v>
       </c>
       <c r="W4">
-        <v>31.64165471453488</v>
+        <v>23.38591497841746</v>
       </c>
       <c r="X4">
-        <v>10.33671436614674</v>
+        <v>8.216535085289586</v>
       </c>
       <c r="Y4">
         <v>0</v>
@@ -831,52 +849,52 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>99.95719444174949</v>
+        <v>99.95878702414677</v>
       </c>
       <c r="D5">
-        <v>99.92869488589152</v>
+        <v>99.91863704418111</v>
       </c>
       <c r="E5">
-        <v>99.91028449765972</v>
+        <v>99.88587801209265</v>
       </c>
       <c r="F5">
-        <v>99.90223815220925</v>
+        <v>99.86833232703056</v>
       </c>
       <c r="G5">
-        <v>99.8968406037083</v>
+        <v>99.85590152806284</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>70.54844602931823</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>57.10395370930667</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>49.55531578907553</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>44.6058886839106</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>41.21038345400878</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>41.23284097667925</v>
+        <v>39.80580448716562</v>
       </c>
       <c r="P5">
-        <v>16.26575266841121</v>
+        <v>20.85904370823853</v>
       </c>
       <c r="Q5">
-        <v>5.051159928617697</v>
+        <v>7.244863936891689</v>
       </c>
       <c r="R5">
-        <v>0.9400401950941967</v>
+        <v>1.554094800740086</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -885,16 +903,16 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>55.46851924088892</v>
+        <v>61.73322884796664</v>
       </c>
       <c r="V5">
-        <v>42.63716876494986</v>
+        <v>33.52366435538025</v>
       </c>
       <c r="W5">
-        <v>23.20622831696753</v>
+        <v>18.44658962725041</v>
       </c>
       <c r="X5">
-        <v>7.581024472045351</v>
+        <v>6.481125689051066</v>
       </c>
       <c r="Y5">
         <v>0</v>
@@ -908,73 +926,73 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>99.09849898267518</v>
+        <v>100.0004750000594</v>
       </c>
       <c r="D6">
-        <v>98.47826682178443</v>
+        <v>99.98582499822813</v>
       </c>
       <c r="E6">
-        <v>98.11434893815326</v>
+        <v>99.97403749675469</v>
       </c>
       <c r="F6">
-        <v>98.03313323730048</v>
+        <v>99.9676312459539</v>
       </c>
       <c r="G6">
-        <v>97.99938268961974</v>
+        <v>99.96407499550938</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>78.40826156014585</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>72.12709532465908</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>68.29346930603116</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>65.51382690705113</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>63.13988668765981</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>77.99537919778342</v>
+        <v>79.46655084821552</v>
       </c>
       <c r="P6">
-        <v>59.60731026324105</v>
+        <v>62.53289023638301</v>
       </c>
       <c r="Q6">
-        <v>49.97778549219008</v>
+        <v>53.52163837379682</v>
       </c>
       <c r="R6">
-        <v>45.03429606199249</v>
+        <v>48.35000569954787</v>
       </c>
       <c r="S6">
-        <v>41.61600189852994</v>
+        <v>44.74268805065912</v>
       </c>
       <c r="T6">
         <v>100</v>
       </c>
       <c r="U6">
-        <v>88.35586730755475</v>
+        <v>90.81982484707055</v>
       </c>
       <c r="V6">
-        <v>82.62539166216337</v>
+        <v>84.93403605190666</v>
       </c>
       <c r="W6">
-        <v>77.81335417100422</v>
+        <v>79.99158087001723</v>
       </c>
       <c r="X6">
-        <v>73.5811136441929</v>
+        <v>75.64240021524952</v>
       </c>
       <c r="Y6">
-        <v>69.78063434291694</v>
+        <v>71.73563434328398</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -985,73 +1003,73 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>99.95532736340486</v>
+        <v>99.96194750493866</v>
       </c>
       <c r="D7">
-        <v>99.92331124502282</v>
+        <v>99.92294463537038</v>
       </c>
       <c r="E7">
-        <v>99.90454511436533</v>
+        <v>99.89186988997852</v>
       </c>
       <c r="F7">
-        <v>99.89665509338649</v>
+        <v>99.8747381389979</v>
       </c>
       <c r="G7">
-        <v>99.89170118472757</v>
+        <v>99.86265212635355</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>68.57349131658499</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>55.50537216798796</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>48.16804916639263</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>43.35717783299641</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>40.05672741200021</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>61.60924407749072</v>
+        <v>64.5290842876547</v>
       </c>
       <c r="P7">
-        <v>37.1757682538381</v>
+        <v>42.89607223439231</v>
       </c>
       <c r="Q7">
-        <v>26.29602307177099</v>
+        <v>31.79009791832477</v>
       </c>
       <c r="R7">
-        <v>21.08870460168396</v>
+        <v>26.06831653040102</v>
       </c>
       <c r="S7">
-        <v>18.69639487611707</v>
+        <v>23.2840287602366</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>80.1398353855718</v>
+        <v>83.55469724142563</v>
       </c>
       <c r="V7">
-        <v>70.57943576795182</v>
+        <v>72.95704604156245</v>
       </c>
       <c r="W7">
-        <v>62.23548476276587</v>
+        <v>64.75084878891811</v>
       </c>
       <c r="X7">
-        <v>56.54333865631337</v>
+        <v>59.22243977226825</v>
       </c>
       <c r="Y7">
-        <v>52.14976929757664</v>
+        <v>54.7803090792103</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1062,37 +1080,37 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>56.01966584959103</v>
+        <v>87.4795881164851</v>
       </c>
       <c r="D8">
-        <v>27.41792068530046</v>
+        <v>69.28776300966335</v>
       </c>
       <c r="E8">
-        <v>12.26573491483414</v>
+        <v>53.19687635367823</v>
       </c>
       <c r="F8">
-        <v>4.905400095428971</v>
+        <v>47.9036654531248</v>
       </c>
       <c r="G8">
-        <v>1.995434813964729</v>
+        <v>44.07094709201023</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>79.31346689909101</v>
+        <v>88.99286942528755</v>
       </c>
       <c r="J8">
-        <v>65.09080157162347</v>
+        <v>80.2252602206319</v>
       </c>
       <c r="K8">
-        <v>57.54496632853125</v>
+        <v>72.9388412827261</v>
       </c>
       <c r="L8">
-        <v>52.80736411267557</v>
+        <v>66.17320760600592</v>
       </c>
       <c r="M8">
-        <v>49.92568927368215</v>
+        <v>59.92946713015477</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1103,37 +1121,37 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>67.9011466381301</v>
+        <v>72.47630089349983</v>
       </c>
       <c r="D9">
-        <v>46.58471275710156</v>
+        <v>45.26858640371246</v>
       </c>
       <c r="E9">
-        <v>34.33587647951938</v>
+        <v>33.01106693934045</v>
       </c>
       <c r="F9">
-        <v>28.7098889629328</v>
+        <v>29.72638909978511</v>
       </c>
       <c r="G9">
-        <v>25.95511894337307</v>
+        <v>27.34801522672277</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>78.58071454117396</v>
+        <v>88.12154681468206</v>
       </c>
       <c r="J9">
-        <v>67.76266924100636</v>
+        <v>79.43977841220362</v>
       </c>
       <c r="K9">
-        <v>61.75498033827819</v>
+        <v>72.22470468762607</v>
       </c>
       <c r="L9">
-        <v>57.75349613198522</v>
+        <v>65.52531283045471</v>
       </c>
       <c r="M9">
-        <v>54.9565724737051</v>
+        <v>59.34270435637509</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1144,37 +1162,37 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>56.24678990284843</v>
+        <v>87.69842259848195</v>
       </c>
       <c r="D10">
-        <v>27.2536262266988</v>
+        <v>68.12972238483661</v>
       </c>
       <c r="E10">
-        <v>11.13526801235201</v>
+        <v>48.20990078942599</v>
       </c>
       <c r="F10">
-        <v>4.290968214201659</v>
+        <v>38.11908459925979</v>
       </c>
       <c r="G10">
-        <v>2.123354056206198</v>
+        <v>32.22944429971925</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>85.74865159904664</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>81.77297449927586</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>80.64733024671197</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>79.86831780511136</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>79.25783877067485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1185,37 +1203,37 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>67.59456337827932</v>
+        <v>87.69842501594073</v>
       </c>
       <c r="D11">
-        <v>46.13324302179626</v>
+        <v>68.12972238483661</v>
       </c>
       <c r="E11">
-        <v>33.88299388782263</v>
+        <v>48.20989958069661</v>
       </c>
       <c r="F11">
-        <v>28.3697888439595</v>
+        <v>38.11908459925979</v>
       </c>
       <c r="G11">
-        <v>25.84789689875555</v>
+        <v>32.22944429971925</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>85.17249987089193</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>77.89198833722089</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>74.15337819135425</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>71.71097312724123</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>70.19805128222545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1226,37 +1244,37 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>56.01966584959103</v>
+        <v>87.4795881164851</v>
       </c>
       <c r="D12">
-        <v>27.41792068530046</v>
+        <v>69.28776300966335</v>
       </c>
       <c r="E12">
-        <v>12.26573491483414</v>
+        <v>53.19687635367823</v>
       </c>
       <c r="F12">
-        <v>4.905400095428971</v>
+        <v>47.9036654531248</v>
       </c>
       <c r="G12">
-        <v>2.089368462929229</v>
+        <v>44.07094709201023</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
-        <v>79.31346689909101</v>
+        <v>88.99286942528755</v>
       </c>
       <c r="J12">
-        <v>65.09080157162347</v>
+        <v>80.2252602206319</v>
       </c>
       <c r="K12">
-        <v>57.54496632853125</v>
+        <v>72.9388412827261</v>
       </c>
       <c r="L12">
-        <v>52.80736411267557</v>
+        <v>66.17320760600592</v>
       </c>
       <c r="M12">
-        <v>49.92568927368215</v>
+        <v>59.92946713015477</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1267,37 +1285,37 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>67.74613462711184</v>
+        <v>77.40247513858628</v>
       </c>
       <c r="D13">
-        <v>46.35645226861938</v>
+        <v>52.66689404505209</v>
       </c>
       <c r="E13">
-        <v>34.10690261073289</v>
+        <v>37.92970712687601</v>
       </c>
       <c r="F13">
-        <v>28.5379382327788</v>
+        <v>32.44242923856968</v>
       </c>
       <c r="G13">
-        <v>25.90090550659596</v>
+        <v>28.92774098916921</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>81.34806519735513</v>
+        <v>88.12154681468206</v>
       </c>
       <c r="J13">
-        <v>72.01513646021441</v>
+        <v>79.43977841220362</v>
       </c>
       <c r="K13">
-        <v>66.96005342280075</v>
+        <v>72.22470468762607</v>
       </c>
       <c r="L13">
-        <v>63.61310606500932</v>
+        <v>65.52531283045471</v>
       </c>
       <c r="M13">
-        <v>61.35522195380542</v>
+        <v>59.34270435637509</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1422,42 +1440,6 @@
       <c r="M16">
         <v>30.81748474550475</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>59.84351941401084</v>
-      </c>
-      <c r="P16">
-        <v>26.04562252367487</v>
-      </c>
-      <c r="Q16">
-        <v>8.451861326738308</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>100</v>
-      </c>
-      <c r="U16">
-        <v>56.40482525249916</v>
-      </c>
-      <c r="V16">
-        <v>31.42452147857309</v>
-      </c>
-      <c r="W16">
-        <v>11.13547128871438</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
@@ -1499,42 +1481,6 @@
       <c r="M17">
         <v>38.58989628223878</v>
       </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>37.90883570137127</v>
-      </c>
-      <c r="P17">
-        <v>15.61148757732332</v>
-      </c>
-      <c r="Q17">
-        <v>5.065961885545182</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
-      <c r="U17">
-        <v>56.40482541406536</v>
-      </c>
-      <c r="V17">
-        <v>31.42452227127864</v>
-      </c>
-      <c r="W17">
-        <v>11.13547188493569</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
@@ -1544,49 +1490,49 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>100.752452828812</v>
+        <v>83.07755673522372</v>
       </c>
       <c r="D18">
-        <v>66.42072340133161</v>
+        <v>71.66611622097568</v>
       </c>
       <c r="E18">
-        <v>0.2177038210602885</v>
+        <v>63.81990607143722</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>57.55693924992317</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>52.38423744569396</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18">
-        <v>4.68167129797101</v>
+        <v>90.07971787944001</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>83.46974608654307</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>79.94274379084644</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>77.53882500947253</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>76.22133784382824</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>62.24403569655826</v>
+        <v>58.92817794501073</v>
       </c>
       <c r="P18">
-        <v>14.84367178601108</v>
+        <v>25.07804556675455</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>7.696842048747859</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1595,16 +1541,16 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>58.61271832129751</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>32.75013226488022</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>11.62144948829498</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -1621,49 +1567,49 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>76.5153924034571</v>
+        <v>76.76468596660739</v>
       </c>
       <c r="D19">
-        <v>42.76387049833041</v>
+        <v>66.22037408579824</v>
       </c>
       <c r="E19">
-        <v>0.1288192818470296</v>
+        <v>58.97038090685987</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>53.18332042210386</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>48.40368379303607</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19">
-        <v>4.681671458588242</v>
+        <v>90.07971439380599</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>83.46974285668183</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>79.94273876271291</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>77.53882200910826</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>76.22133295969449</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>42.01881645123385</v>
+        <v>44.19486301895058</v>
       </c>
       <c r="P19">
-        <v>8.504173913043477</v>
+        <v>18.80799295659727</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>5.772465592041804</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1672,16 +1618,16 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>58.61271854804117</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>32.75013246891492</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>11.62145012333095</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -1704,66 +1650,30 @@
         <v>66.42072340133161</v>
       </c>
       <c r="E20">
-        <v>10.14358136010216</v>
+        <v>0.2177038210602885</v>
       </c>
       <c r="F20">
-        <v>9.148140949416872</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>8.325988037690335</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
       <c r="I20">
-        <v>12.94431918936486</v>
+        <v>4.68167129797101</v>
       </c>
       <c r="J20">
-        <v>11.99447624209376</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>11.48765134774604</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>11.14221185543925</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>10.95289094279145</v>
-      </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
-      <c r="O20">
-        <v>59.84351941401084</v>
-      </c>
-      <c r="P20">
-        <v>26.04562252367487</v>
-      </c>
-      <c r="Q20">
-        <v>8.451861326738308</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>100</v>
-      </c>
-      <c r="U20">
-        <v>56.40482525249916</v>
-      </c>
-      <c r="V20">
-        <v>31.42452147857309</v>
-      </c>
-      <c r="W20">
-        <v>11.13547128871438</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
         <v>0</v>
       </c>
     </row>
@@ -1775,72 +1685,36 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>62.49320854850934</v>
+        <v>76.5153924034571</v>
       </c>
       <c r="D21">
-        <v>32.49185939605893</v>
+        <v>42.76387049833041</v>
       </c>
       <c r="E21">
-        <v>8.294140596793241</v>
+        <v>0.1288192818470296</v>
       </c>
       <c r="F21">
-        <v>6.230128734810967</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>5.219391398223099</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>30.79349812067632</v>
+        <v>4.681671458588242</v>
       </c>
       <c r="J21">
-        <v>21.81979851600247</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>20.42404024425369</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>19.44309385849737</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>18.84363574529423</v>
-      </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21">
-        <v>39.6102233951017</v>
-      </c>
-      <c r="P21">
-        <v>12.66930640304317</v>
-      </c>
-      <c r="Q21">
-        <v>2.968829961920575</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>100</v>
-      </c>
-      <c r="U21">
-        <v>56.40482541406536</v>
-      </c>
-      <c r="V21">
-        <v>31.42452227127864</v>
-      </c>
-      <c r="W21">
-        <v>11.13547188493569</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
         <v>0</v>
       </c>
     </row>
@@ -1849,40 +1723,76 @@
         <v>45</v>
       </c>
       <c r="B22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>99.15967987768202</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>98.50498979368403</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>98.06173985529017</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>97.71416631011765</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>97.4293954346456</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>99.73259135340375</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>99.54772366135261</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>99.4256046066112</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>99.33851579706582</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>99.2832293011502</v>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
+        <v>51.18717758866439</v>
+      </c>
+      <c r="P22">
+        <v>1.850104701198886</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -1890,40 +1800,394 @@
         <v>46</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>99.15793288538013</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>98.5016879868879</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>98.05788129893365</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>97.71018211974585</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>97.42537922568091</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>99.73200943573667</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>99.5468888379875</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>99.42463235929864</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>99.33742601893479</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>99.28207739442992</v>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
+        <v>33.65832668355958</v>
+      </c>
+      <c r="P23">
+        <v>1.216543530074014</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>100.752452828812</v>
+      </c>
+      <c r="D24">
+        <v>66.42072340133161</v>
+      </c>
+      <c r="E24">
+        <v>10.14358136010216</v>
+      </c>
+      <c r="F24">
+        <v>9.148140949416872</v>
+      </c>
+      <c r="G24">
+        <v>8.325988037690335</v>
+      </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>12.94431918936486</v>
+      </c>
+      <c r="J24">
+        <v>11.99447624209376</v>
+      </c>
+      <c r="K24">
+        <v>11.48765134774604</v>
+      </c>
+      <c r="L24">
+        <v>11.14221185543925</v>
+      </c>
+      <c r="M24">
+        <v>10.95289094279145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>62.49320854850934</v>
+      </c>
+      <c r="D25">
+        <v>32.49185939605893</v>
+      </c>
+      <c r="E25">
+        <v>8.294140596793241</v>
+      </c>
+      <c r="F25">
+        <v>6.230128734810967</v>
+      </c>
+      <c r="G25">
+        <v>5.219391398223099</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>30.79349812067632</v>
+      </c>
+      <c r="J25">
+        <v>21.81979851600247</v>
+      </c>
+      <c r="K25">
+        <v>20.42404024425369</v>
+      </c>
+      <c r="L25">
+        <v>19.44309385849737</v>
+      </c>
+      <c r="M25">
+        <v>18.84363574529423</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26">
+        <v>100</v>
+      </c>
+      <c r="C26">
+        <v>83.07755673522372</v>
+      </c>
+      <c r="D26">
+        <v>71.66611622097568</v>
+      </c>
+      <c r="E26">
+        <v>63.81990607143722</v>
+      </c>
+      <c r="F26">
+        <v>57.55693924992317</v>
+      </c>
+      <c r="G26">
+        <v>52.38423744569396</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>90.07971787944001</v>
+      </c>
+      <c r="J26">
+        <v>83.46974608654307</v>
+      </c>
+      <c r="K26">
+        <v>79.94274379084644</v>
+      </c>
+      <c r="L26">
+        <v>77.53882500947253</v>
+      </c>
+      <c r="M26">
+        <v>76.22133784382824</v>
+      </c>
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
+        <v>58.92817794501073</v>
+      </c>
+      <c r="P26">
+        <v>25.07804556675455</v>
+      </c>
+      <c r="Q26">
+        <v>7.696842048747859</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>100</v>
+      </c>
+      <c r="U26">
+        <v>58.61271832129751</v>
+      </c>
+      <c r="V26">
+        <v>32.75013226488022</v>
+      </c>
+      <c r="W26">
+        <v>11.62144948829498</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27">
+        <v>100</v>
+      </c>
+      <c r="C27">
+        <v>76.76468596660739</v>
+      </c>
+      <c r="D27">
+        <v>66.22037408579824</v>
+      </c>
+      <c r="E27">
+        <v>58.97038090685987</v>
+      </c>
+      <c r="F27">
+        <v>53.18332042210386</v>
+      </c>
+      <c r="G27">
+        <v>48.40368379303607</v>
+      </c>
+      <c r="H27">
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>90.07971439380599</v>
+      </c>
+      <c r="J27">
+        <v>83.46974285668183</v>
+      </c>
+      <c r="K27">
+        <v>79.94273876271291</v>
+      </c>
+      <c r="L27">
+        <v>77.53882200910826</v>
+      </c>
+      <c r="M27">
+        <v>76.22133295969449</v>
+      </c>
+      <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
+        <v>40.8199832537788</v>
+      </c>
+      <c r="P27">
+        <v>13.17340891655028</v>
+      </c>
+      <c r="Q27">
+        <v>3.923530832867923</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>100</v>
+      </c>
+      <c r="U27">
+        <v>58.61271854804117</v>
+      </c>
+      <c r="V27">
+        <v>32.75013246891492</v>
+      </c>
+      <c r="W27">
+        <v>11.62145012333095</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>99.43560437746159</v>
+      </c>
+      <c r="D28">
+        <v>98.93414653493953</v>
+      </c>
+      <c r="E28">
+        <v>98.53448292541044</v>
+      </c>
+      <c r="F28">
+        <v>98.20846922343203</v>
+      </c>
+      <c r="G28">
+        <v>97.93915047217845</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>99.78962002017256</v>
+      </c>
+      <c r="J28">
+        <v>99.63361921923588</v>
+      </c>
+      <c r="K28">
+        <v>99.52075936438177</v>
+      </c>
+      <c r="L28">
+        <v>99.44091427145015</v>
+      </c>
+      <c r="M28">
+        <v>99.39244857478209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+      <c r="C29">
+        <v>99.43418588034584</v>
+      </c>
+      <c r="D29">
+        <v>98.93193944790505</v>
+      </c>
+      <c r="E29">
+        <v>98.53210762264136</v>
+      </c>
+      <c r="F29">
+        <v>98.2060179904957</v>
+      </c>
+      <c r="G29">
+        <v>97.93664302352182</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29">
+        <v>99.78897518870488</v>
+      </c>
+      <c r="J29">
+        <v>99.63274731679762</v>
+      </c>
+      <c r="K29">
+        <v>99.51977773349338</v>
+      </c>
+      <c r="L29">
+        <v>99.43980616131992</v>
+      </c>
+      <c r="M29">
+        <v>99.39126126641386</v>
       </c>
     </row>
   </sheetData>

--- a/verification/model_verification_results_57_buses.xlsx
+++ b/verification/model_verification_results_57_buses.xlsx
@@ -615,22 +615,22 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>100.0004750000594</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>99.98582499822813</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>99.97403749675469</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>99.9676312459539</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>99.96407499550938</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -654,37 +654,37 @@
         <v>100</v>
       </c>
       <c r="O2">
-        <v>79.46655084821552</v>
+        <v>28.02910546328492</v>
       </c>
       <c r="P2">
-        <v>62.53289023638301</v>
+        <v>6.236349885092852</v>
       </c>
       <c r="Q2">
-        <v>53.52163837379682</v>
+        <v>2.122461760657497</v>
       </c>
       <c r="R2">
-        <v>48.35000569954787</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>44.74268805065912</v>
+        <v>0</v>
       </c>
       <c r="T2">
         <v>100</v>
       </c>
       <c r="U2">
-        <v>90.81982484707055</v>
+        <v>64.93214093947304</v>
       </c>
       <c r="V2">
-        <v>84.93403605190666</v>
+        <v>35.32793145586847</v>
       </c>
       <c r="W2">
-        <v>79.99158087001723</v>
+        <v>9.69252809716899</v>
       </c>
       <c r="X2">
-        <v>75.64240021524952</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>71.73563434328398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -692,22 +692,22 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>99.96511377753832</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>99.92726410177075</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>99.89786714513725</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>99.88114926720489</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>99.86940799018285</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -731,37 +731,37 @@
         <v>100</v>
       </c>
       <c r="O3">
-        <v>69.47526776288542</v>
+        <v>33.78202316483077</v>
       </c>
       <c r="P3">
-        <v>47.30484666381318</v>
+        <v>5.245657751312715</v>
       </c>
       <c r="Q3">
-        <v>36.70065875425671</v>
+        <v>1.785292424978698</v>
       </c>
       <c r="R3">
-        <v>30.972673123466</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>27.94227133682903</v>
+        <v>0</v>
       </c>
       <c r="T3">
         <v>100</v>
       </c>
       <c r="U3">
-        <v>85.11255360273513</v>
+        <v>64.93214238599123</v>
       </c>
       <c r="V3">
-        <v>75.77223754692515</v>
+        <v>35.32793145586847</v>
       </c>
       <c r="W3">
-        <v>68.05655786667185</v>
+        <v>9.692528458798535</v>
       </c>
       <c r="X3">
-        <v>62.98769990238596</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>58.6911341197496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -772,19 +772,19 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>99.96426700801663</v>
+        <v>57.72461468935558</v>
       </c>
       <c r="D4">
-        <v>99.9471536737416</v>
+        <v>21.66222262299586</v>
       </c>
       <c r="E4">
-        <v>99.93454055885225</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>99.92809649470412</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>99.92443381614854</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -849,19 +849,19 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>99.95878702414677</v>
+        <v>43.28548027253527</v>
       </c>
       <c r="D5">
-        <v>99.91863704418111</v>
+        <v>16.24367158516955</v>
       </c>
       <c r="E5">
-        <v>99.88587801209265</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>99.86833232703056</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>99.85590152806284</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -926,19 +926,19 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>100.0004750000594</v>
+        <v>57.72461468935558</v>
       </c>
       <c r="D6">
-        <v>99.98582499822813</v>
+        <v>21.66222262299586</v>
       </c>
       <c r="E6">
-        <v>99.97403749675469</v>
+        <v>7.542130163120694</v>
       </c>
       <c r="F6">
-        <v>99.9676312459539</v>
+        <v>14.71297384637484</v>
       </c>
       <c r="G6">
-        <v>99.96407499550938</v>
+        <v>18.0615576941023</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -962,37 +962,37 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>79.46655084821552</v>
+        <v>61.38507893942833</v>
       </c>
       <c r="P6">
-        <v>62.53289023638301</v>
+        <v>31.54625925713376</v>
       </c>
       <c r="Q6">
-        <v>53.52163837379682</v>
+        <v>11.39152018505137</v>
       </c>
       <c r="R6">
-        <v>48.35000569954787</v>
+        <v>2.63407953418042</v>
       </c>
       <c r="S6">
-        <v>44.74268805065912</v>
+        <v>0</v>
       </c>
       <c r="T6">
         <v>100</v>
       </c>
       <c r="U6">
-        <v>90.81982484707055</v>
+        <v>61.1870441876865</v>
       </c>
       <c r="V6">
-        <v>84.93403605190666</v>
+        <v>40.10501855813961</v>
       </c>
       <c r="W6">
-        <v>79.99158087001723</v>
+        <v>23.38591497841746</v>
       </c>
       <c r="X6">
-        <v>75.64240021524952</v>
+        <v>8.216535085289586</v>
       </c>
       <c r="Y6">
-        <v>71.73563434328398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1003,19 +1003,19 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>99.96194750493866</v>
+        <v>43.28548027253527</v>
       </c>
       <c r="D7">
-        <v>99.92294463537038</v>
+        <v>16.24367158516955</v>
       </c>
       <c r="E7">
-        <v>99.89186988997852</v>
+        <v>5.655554874542537</v>
       </c>
       <c r="F7">
-        <v>99.8747381389979</v>
+        <v>11.03269561521557</v>
       </c>
       <c r="G7">
-        <v>99.86265212635355</v>
+        <v>13.54367108393087</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1039,37 +1039,37 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>64.5290842876547</v>
+        <v>37.3224615677554</v>
       </c>
       <c r="P7">
-        <v>42.89607223439231</v>
+        <v>14.42232739877371</v>
       </c>
       <c r="Q7">
-        <v>31.79009791832477</v>
+        <v>4.994121202780937</v>
       </c>
       <c r="R7">
-        <v>26.06831653040102</v>
+        <v>0.9134095139840013</v>
       </c>
       <c r="S7">
-        <v>23.2840287602366</v>
+        <v>0</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>83.55469724142563</v>
+        <v>62.66054830747301</v>
       </c>
       <c r="V7">
-        <v>72.95704604156245</v>
+        <v>34.04669490756996</v>
       </c>
       <c r="W7">
-        <v>64.75084878891811</v>
+        <v>15.90892520025107</v>
       </c>
       <c r="X7">
-        <v>59.22243977226825</v>
+        <v>4.602348857275958</v>
       </c>
       <c r="Y7">
-        <v>54.7803090792103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1080,19 +1080,19 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>87.4795881164851</v>
+        <v>90.19397156663072</v>
       </c>
       <c r="D8">
-        <v>69.28776300966335</v>
+        <v>82.11152924513442</v>
       </c>
       <c r="E8">
-        <v>53.19687635367823</v>
+        <v>75.79430139599138</v>
       </c>
       <c r="F8">
-        <v>47.9036654531248</v>
+        <v>69.86162415646402</v>
       </c>
       <c r="G8">
-        <v>44.07094709201023</v>
+        <v>64.04375495563104</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -1121,19 +1121,19 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>72.47630089349983</v>
+        <v>89.30792092285238</v>
       </c>
       <c r="D9">
-        <v>45.26858640371246</v>
+        <v>79.19735186667833</v>
       </c>
       <c r="E9">
-        <v>33.01106693934045</v>
+        <v>69.93058494129129</v>
       </c>
       <c r="F9">
-        <v>29.72638909978511</v>
+        <v>61.2148042493928</v>
       </c>
       <c r="G9">
-        <v>27.34801522672277</v>
+        <v>53.72490772928163</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -1162,19 +1162,19 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>87.69842259848195</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>68.12972238483661</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>48.20990078942599</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>38.11908459925979</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>32.22944429971925</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1203,19 +1203,19 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>87.69842501594073</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>68.12972238483661</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>48.20989958069661</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>38.11908459925979</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>32.22944429971925</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1244,19 +1244,19 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>87.4795881164851</v>
+        <v>90.19397156663072</v>
       </c>
       <c r="D12">
-        <v>69.28776300966335</v>
+        <v>82.11152924513442</v>
       </c>
       <c r="E12">
-        <v>53.19687635367823</v>
+        <v>75.79430139599138</v>
       </c>
       <c r="F12">
-        <v>47.9036654531248</v>
+        <v>69.86162415646402</v>
       </c>
       <c r="G12">
-        <v>44.07094709201023</v>
+        <v>64.04375495563104</v>
       </c>
       <c r="H12">
         <v>100</v>
@@ -1285,19 +1285,19 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>77.40247513858628</v>
+        <v>87.46953576163094</v>
       </c>
       <c r="D13">
-        <v>52.66689404505209</v>
+        <v>77.56709068743191</v>
       </c>
       <c r="E13">
-        <v>37.92970712687601</v>
+        <v>68.49107825091988</v>
       </c>
       <c r="F13">
-        <v>32.44242923856968</v>
+        <v>59.9547101097434</v>
       </c>
       <c r="G13">
-        <v>28.92774098916921</v>
+        <v>52.61899156712148</v>
       </c>
       <c r="H13">
         <v>100</v>
@@ -1603,13 +1603,13 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>44.19486301895058</v>
+        <v>34.55520196398833</v>
       </c>
       <c r="P19">
-        <v>18.80799295659727</v>
+        <v>11.5500997748341</v>
       </c>
       <c r="Q19">
-        <v>5.772465592041804</v>
+        <v>3.544905279831729</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1762,10 +1762,10 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>51.18717758866439</v>
+        <v>45.77737587673744</v>
       </c>
       <c r="P22">
-        <v>1.850104701198886</v>
+        <v>1.654573319097321</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -1839,10 +1839,10 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>33.65832668355958</v>
+        <v>27.76606102442316</v>
       </c>
       <c r="P23">
-        <v>1.216543530074014</v>
+        <v>0.4694027890108645</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -2075,13 +2075,13 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>40.8199832537788</v>
+        <v>31.64553800537269</v>
       </c>
       <c r="P27">
-        <v>13.17340891655028</v>
+        <v>6.801176979031956</v>
       </c>
       <c r="Q27">
-        <v>3.923530832867923</v>
+        <v>2.025643305090031</v>
       </c>
       <c r="R27">
         <v>0</v>
